--- a/小野町_引継ぎ_整理済/07_介護保険_見える化整理/小野町_第10期介護保険事業計画_供給体制・介護予防整理.xlsx
+++ b/小野町_引継ぎ_整理済/07_介護保険_見える化整理/小野町_第10期介護保険事業計画_供給体制・介護予防整理.xlsx
@@ -547,7 +547,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>参考として新地町の週1回以上参加率は平成29年度17.8％、令和2年度15.3％。本町は0.0％</t>
+          <t>本町の週1回以上参加率は令和2年度0.0％で、県内59市町村中38位。中央値0.9％、最大15.3％、0％の団体が22</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
